--- a/public/templates/storyboard-template.xlsx
+++ b/public/templates/storyboard-template.xlsx
@@ -1,58 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21f6c6e03fe5d384/01_創作/02_漫画/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="157" documentId="8_{35EADB1E-2E44-4053-A80B-98B0B1921AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C245F4-226E-4A8D-9641-F0A982A61F3D}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1AF87EC8-E642-4994-92CA-5503D747740F}"/>
+  </bookViews>
   <sheets>
     <sheet name="文字ネーム" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>感情</t>
+  </si>
+  <si>
+    <t>大きさ</t>
+  </si>
+  <si>
+    <t>役割</t>
+  </si>
+  <si>
+    <t>形</t>
+  </si>
+  <si>
+    <t>カメラ</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>１ページ目</t>
+  </si>
+  <si>
+    <t>顔サイズ</t>
+    <rPh sb="0" eb="1">
+      <t>カオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,23 +122,243 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -86,44 +368,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -151,14 +433,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -186,6 +485,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -197,180 +513,136 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -392,45 +664,157 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21230B67-6EC1-4EED-9BBD-A7D3D832D00C}">
   <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="6" width="8.88671875" style="3"/>
+    <col min="7" max="7" width="64.77734375" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="3"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>感情</v>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="str">
-        <v>大きさ</v>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" t="str">
-        <v>役割</v>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" t="str">
-        <v>形</v>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
-      <c r="E1" t="str">
-        <v>カメラ</v>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
-      <c r="F1" t="str">
-        <v>顔サイズ</v>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
       </c>
-      <c r="G1" t="str">
-        <v>内容</v>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>１ページ目</v>
+    <row r="2" spans="1:7" s="5" customFormat="1">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
       </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="A1:B1048576 F1:F1048576">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+      <formula>"小"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+      <formula>"中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="21" operator="equal">
+      <formula>"大"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:G1048576">
+    <cfRule type="expression" dxfId="14" priority="25">
+      <formula>IF($G1="",TRUE)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576 F1:F1048576">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
+      <formula>"極大"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+      <formula>"極小"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+      <formula>"場、時"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+      <formula>"時"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
+      <formula>"予"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
+      <formula>"場"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+      <formula>"縦"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1:F1048576">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+      <formula>"正"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
+      <formula>"横"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:F1048576">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"下"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"上"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"煽"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"俯"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
-  </ignoredErrors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="17" operator="containsText" id="{2607ED0D-EBAF-4D19-B655-ABCA814D0F11}">
+            <xm:f>NOT(ISERROR(SEARCH("魅",C1)))</xm:f>
+            <xm:f>"魅"</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C1:C1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/public/templates/storyboard-template.xlsx
+++ b/public/templates/storyboard-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21f6c6e03fe5d384/01_創作/02_漫画/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="157" documentId="8_{35EADB1E-2E44-4053-A80B-98B0B1921AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05C245F4-226E-4A8D-9641-F0A982A61F3D}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{35EADB1E-2E44-4053-A80B-98B0B1921AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84342BA0-E6F9-4100-A382-8DFF38DA1E92}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1AF87EC8-E642-4994-92CA-5503D747740F}"/>
   </bookViews>
@@ -166,7 +166,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="36">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -304,6 +304,183 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -728,67 +905,67 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:B1048576 F1:F1048576">
-    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="19" operator="equal">
       <formula>"小"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="20" operator="equal">
       <formula>"中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="21" operator="equal">
       <formula>"大"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:G1048576">
-    <cfRule type="expression" dxfId="14" priority="25">
+    <cfRule type="expression" dxfId="32" priority="25">
       <formula>IF($G1="",TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576 F1:F1048576">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
-      <formula>"極大"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+      <formula>"特大"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="31" priority="4" operator="equal">
       <formula>"極小"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="5" operator="equal">
       <formula>"場、時"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="6" operator="equal">
       <formula>"時"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="16" operator="equal">
       <formula>"予"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="18" operator="equal">
       <formula>"場"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="10" operator="equal">
       <formula>"縦"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:F1048576">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="8" operator="equal">
       <formula>"正"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
       <formula>"横"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:F1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"下"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"上"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="14" operator="equal">
       <formula>"煽"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="15" operator="equal">
       <formula>"俯"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/public/templates/storyboard-template.xlsx
+++ b/public/templates/storyboard-template.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21f6c6e03fe5d384/01_創作/02_漫画/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="8_{35EADB1E-2E44-4053-A80B-98B0B1921AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84342BA0-E6F9-4100-A382-8DFF38DA1E92}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="8_{35EADB1E-2E44-4053-A80B-98B0B1921AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBEC2A8A-7125-4B88-BF75-5D404474B5BE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1AF87EC8-E642-4994-92CA-5503D747740F}"/>
   </bookViews>
   <sheets>
     <sheet name="文字ネーム" sheetId="1" r:id="rId1"/>
+    <sheet name="JSON" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -166,7 +167,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -304,183 +305,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -905,67 +729,67 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:B1048576 F1:F1048576">
-    <cfRule type="cellIs" dxfId="35" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="19" operator="equal">
       <formula>"小"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="20" operator="equal">
       <formula>"中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="21" operator="equal">
       <formula>"大"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:G1048576">
-    <cfRule type="expression" dxfId="32" priority="25">
+    <cfRule type="expression" dxfId="14" priority="25">
       <formula>IF($G1="",TRUE)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576 F1:F1048576">
-    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
       <formula>"特大"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <formula>"極小"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="30" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"場、時"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"時"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
       <formula>"予"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
       <formula>"場"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="25" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>"縦"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:F1048576">
-    <cfRule type="cellIs" dxfId="24" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"正"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
       <formula>"横"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:F1048576">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"下"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"上"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
       <formula>"煽"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
       <formula>"俯"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -994,4 +818,14 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7B2F5B7-A4C5-4E03-B689-25F77E61D115}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>